--- a/1er Entrega/Excel TP4 - G5.xlsx
+++ b/1er Entrega/Excel TP4 - G5.xlsx
@@ -1,26 +1,273 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc_ju\OneDrive\Escritorio\Tp4-Simulacion-G5\1er Entrega\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35DBF18D-9B94-4EF8-9C77-7DC8C70A5670}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={2AC92C0D-91E0-4D44-A3F2-EF4B8018F531}</author>
+    <author>tc={8099394A-7DAB-4E3F-B9F6-5B67BC2399FA}</author>
+  </authors>
+  <commentList>
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{2AC92C0D-91E0-4D44-A3F2-EF4B8018F531}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Si el técnico estaba realizando una reparación en ese momento, debe interrumpirla, atender al cliente y, una vez que este se retira, retomar la reparación desde el punto exacto en el que la dejó. 
+</t>
+      </text>
+    </comment>
+    <comment ref="T16" authorId="1" shapeId="0" xr:uid="{8099394A-7DAB-4E3F-B9F6-5B67BC2399FA}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Cuando tengo un equipo interrumpido</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="65">
+  <si>
+    <t>Eventos</t>
+  </si>
+  <si>
+    <t>RND</t>
+  </si>
+  <si>
+    <t>Proxima llegada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fin atencion </t>
+  </si>
+  <si>
+    <t>Estado</t>
+  </si>
+  <si>
+    <t>Cliente</t>
+  </si>
+  <si>
+    <t>Horario Apertura</t>
+  </si>
+  <si>
+    <t>hs</t>
+  </si>
+  <si>
+    <t>Horario Cierre</t>
+  </si>
+  <si>
+    <t>Local</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clientes </t>
+  </si>
+  <si>
+    <t>Llegada  Exp.Neg media</t>
+  </si>
+  <si>
+    <t>min</t>
+  </si>
+  <si>
+    <t>U(10, 20)</t>
+  </si>
+  <si>
+    <t>demora</t>
+  </si>
+  <si>
+    <t>Atencion cliente</t>
+  </si>
+  <si>
+    <t>Reparacion en taller</t>
+  </si>
+  <si>
+    <t>reparación  Exp.Neg media</t>
+  </si>
+  <si>
+    <t>Presupuesto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acepta </t>
+  </si>
+  <si>
+    <t>Rechaza</t>
+  </si>
+  <si>
+    <t>P()</t>
+  </si>
+  <si>
+    <t>P()Ac</t>
+  </si>
+  <si>
+    <t>0.5</t>
+  </si>
+  <si>
+    <t>Tiempo reparacion Equipo</t>
+  </si>
+  <si>
+    <t>Porcentaje tiempo  reparacion
+reparaciones</t>
+  </si>
+  <si>
+    <t>llegada_Cliente</t>
+  </si>
+  <si>
+    <t>Tiempo entre llegadas min</t>
+  </si>
+  <si>
+    <t>Fin Reparación</t>
+  </si>
+  <si>
+    <t>Tiempo Reparación</t>
+  </si>
+  <si>
+    <t>Estadistica</t>
+  </si>
+  <si>
+    <t>Cant Clientes no atendidos por cierre 18:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tiempo acumulado </t>
+  </si>
+  <si>
+    <t>Equipo en taller</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tiempo </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prom tiempo </t>
+  </si>
+  <si>
+    <t>Reparacion Equipo</t>
+  </si>
+  <si>
+    <t>Clientes Perdidos</t>
+  </si>
+  <si>
+    <t>Acu  Clientes no atendidos</t>
+  </si>
+  <si>
+    <t>Reloj(min)</t>
+  </si>
+  <si>
+    <t>Atención_Cliente</t>
+  </si>
+  <si>
+    <t>Reparacion_taller</t>
+  </si>
+  <si>
+    <t>Tecnico</t>
+  </si>
+  <si>
+    <t>Cola Clientes</t>
+  </si>
+  <si>
+    <t>Cola Equipos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tiempo faltante de reparacion </t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Hora ingreso</t>
+  </si>
+  <si>
+    <t>Equipos</t>
+  </si>
+  <si>
+    <t>Inicializacion</t>
+  </si>
+  <si>
+    <t>Stock de equipos para retirar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cantidad de Equipos reparados </t>
+  </si>
+  <si>
+    <t>AC Tiempos de Reparacion</t>
+  </si>
+  <si>
+    <t>libre</t>
+  </si>
+  <si>
+    <t>Atendiendo_Client</t>
+  </si>
+  <si>
+    <t>atentido</t>
+  </si>
+  <si>
+    <t>Atención_Cliente(Diagnóstico)</t>
+  </si>
+  <si>
+    <t>Tiempo atencion (min)</t>
+  </si>
+  <si>
+    <t>Decision</t>
+  </si>
+  <si>
+    <t>Presupuesto elevado</t>
+  </si>
+  <si>
+    <t>Si</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>P() AC</t>
+  </si>
+  <si>
+    <t>realizar la reparación</t>
+  </si>
+  <si>
+    <t>Reparando_Equipo</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -28,19 +275,181 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="4"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="7">
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -49,8 +458,126 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -66,6 +593,12 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Junior Jesus Quispe Ricra" id="{D101D665-75E1-4165-A0CF-365C2FBB2EC6}" userId="S::97139@sistemas.frc.utn.edu.ar::03d9ef1a-078f-46ef-a228-08e1671e3a99" providerId="AD"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -329,10 +862,1028 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="E1" dT="2026-05-12T13:08:23.33" personId="{D101D665-75E1-4165-A0CF-365C2FBB2EC6}" id="{2AC92C0D-91E0-4D44-A3F2-EF4B8018F531}">
+    <text xml:space="preserve">Si el técnico estaba realizando una reparación en ese momento, debe interrumpirla, atender al cliente y, una vez que este se retira, retomar la reparación desde el punto exacto en el que la dejó. 
+</text>
+  </threadedComment>
+  <threadedComment ref="T16" dT="2026-05-12T21:23:25.97" personId="{D101D665-75E1-4165-A0CF-365C2FBB2EC6}" id="{8099394A-7DAB-4E3F-B9F6-5B67BC2399FA}">
+    <text>Cuando tengo un equipo interrumpido</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:BA34"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="16.453125" style="6" customWidth="1"/>
+    <col min="2" max="2" width="11.08984375" style="6" customWidth="1"/>
+    <col min="3" max="3" width="11" style="6" customWidth="1"/>
+    <col min="4" max="4" width="14" style="6" customWidth="1"/>
+    <col min="5" max="5" width="13.453125" style="6" customWidth="1"/>
+    <col min="6" max="7" width="8.7265625" style="6"/>
+    <col min="8" max="9" width="11.26953125" style="6" customWidth="1"/>
+    <col min="10" max="10" width="12.453125" style="6" customWidth="1"/>
+    <col min="11" max="12" width="11.26953125" style="6" customWidth="1"/>
+    <col min="13" max="13" width="11" style="6" customWidth="1"/>
+    <col min="14" max="14" width="11.6328125" style="6" customWidth="1"/>
+    <col min="15" max="15" width="13.1796875" style="6" customWidth="1"/>
+    <col min="16" max="16" width="20.6328125" style="6" customWidth="1"/>
+    <col min="17" max="17" width="10.81640625" style="6" customWidth="1"/>
+    <col min="18" max="18" width="8.7265625" style="6"/>
+    <col min="19" max="19" width="13.36328125" style="6" customWidth="1"/>
+    <col min="20" max="20" width="13" style="6" customWidth="1"/>
+    <col min="21" max="21" width="1.81640625" style="6" customWidth="1"/>
+    <col min="22" max="22" width="15.08984375" style="6" customWidth="1"/>
+    <col min="23" max="23" width="22.36328125" style="6" customWidth="1"/>
+    <col min="24" max="24" width="1.453125" style="6" customWidth="1"/>
+    <col min="25" max="25" width="2.1796875" style="6" customWidth="1"/>
+    <col min="26" max="28" width="8.7265625" style="6"/>
+    <col min="29" max="29" width="14.7265625" style="6" customWidth="1"/>
+    <col min="30" max="30" width="12.7265625" style="6" customWidth="1"/>
+    <col min="31" max="31" width="10.453125" style="6" customWidth="1"/>
+    <col min="32" max="32" width="2.26953125" style="6" customWidth="1"/>
+    <col min="33" max="33" width="12.36328125" style="6" customWidth="1"/>
+    <col min="34" max="34" width="12.90625" style="6" customWidth="1"/>
+    <col min="35" max="35" width="12.26953125" style="6" customWidth="1"/>
+    <col min="36" max="43" width="8.7265625" style="6"/>
+    <col min="44" max="44" width="25.36328125" style="6" customWidth="1"/>
+    <col min="45" max="45" width="16.7265625" style="6" customWidth="1"/>
+    <col min="46" max="48" width="8.7265625" style="6"/>
+    <col min="49" max="49" width="17.1796875" style="6" customWidth="1"/>
+    <col min="50" max="50" width="16.7265625" style="6" customWidth="1"/>
+    <col min="51" max="16384" width="8.7265625" style="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:53" ht="29" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:53" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="8">
+        <v>10</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="N2" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="O2" s="8">
+        <v>90</v>
+      </c>
+      <c r="P2" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:53" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="8">
+        <v>18</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="AQ3" s="15"/>
+      <c r="AR3" s="15"/>
+      <c r="AS3" s="15"/>
+      <c r="AT3" s="15"/>
+    </row>
+    <row r="4" spans="1:53" x14ac:dyDescent="0.35">
+      <c r="AQ4" s="15"/>
+      <c r="AR4" s="15"/>
+      <c r="AS4" s="15"/>
+      <c r="AT4" s="15"/>
+    </row>
+    <row r="5" spans="1:53" x14ac:dyDescent="0.35">
+      <c r="N5" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AQ5" s="15"/>
+      <c r="AR5" s="15"/>
+      <c r="AS5" s="15"/>
+      <c r="AT5" s="15"/>
+    </row>
+    <row r="6" spans="1:53" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="N6" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="O6" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="P6" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="AQ6" s="15"/>
+      <c r="AR6" s="15"/>
+      <c r="AS6" s="15"/>
+      <c r="AT6" s="15"/>
+    </row>
+    <row r="7" spans="1:53" ht="29" x14ac:dyDescent="0.35">
+      <c r="A7" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="8">
+        <v>45</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="N7" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="O7" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="P7" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="AQ7" s="15"/>
+      <c r="AR7" s="22"/>
+      <c r="AS7" s="22"/>
+      <c r="AT7" s="22"/>
+    </row>
+    <row r="8" spans="1:53" ht="34" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E8" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F8" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="G8" s="8">
+        <f>F8</f>
+        <v>0.3</v>
+      </c>
+      <c r="N8" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="O8" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="P8" s="8">
+        <v>1</v>
+      </c>
+      <c r="AQ8" s="15"/>
+      <c r="AR8" s="22"/>
+      <c r="AS8" s="22"/>
+      <c r="AT8" s="22"/>
+    </row>
+    <row r="9" spans="1:53" x14ac:dyDescent="0.35">
+      <c r="E9" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F9" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="G9" s="8">
+        <f>G8+F9</f>
+        <v>1</v>
+      </c>
+      <c r="AQ9" s="15"/>
+      <c r="AR9" s="22"/>
+      <c r="AS9" s="22"/>
+      <c r="AT9" s="22"/>
+    </row>
+    <row r="10" spans="1:53" x14ac:dyDescent="0.35">
+      <c r="AX10" s="15"/>
+      <c r="AY10" s="15"/>
+      <c r="AZ10" s="15"/>
+      <c r="BA10" s="15"/>
+    </row>
+    <row r="12" spans="1:53" x14ac:dyDescent="0.35">
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
+    </row>
+    <row r="13" spans="1:53" x14ac:dyDescent="0.35">
+      <c r="B13" s="11">
+        <f ca="1">RAND()</f>
+        <v>0.85600868159281895</v>
+      </c>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
+    </row>
+    <row r="14" spans="1:53" x14ac:dyDescent="0.35">
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="33" t="s">
+        <v>58</v>
+      </c>
+      <c r="J14" s="15"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="15"/>
+      <c r="Z14" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA14" s="23"/>
+      <c r="AB14" s="23"/>
+      <c r="AC14" s="23"/>
+      <c r="AD14" s="23"/>
+      <c r="AE14" s="23"/>
+      <c r="AG14" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="AR14" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:53" x14ac:dyDescent="0.35">
+      <c r="C15" s="1"/>
+      <c r="D15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" s="1"/>
+      <c r="F15" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="32"/>
+      <c r="K15" s="32"/>
+      <c r="L15" s="32"/>
+      <c r="M15" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="N15" s="13"/>
+      <c r="O15" s="13"/>
+      <c r="P15" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q15" s="21"/>
+      <c r="R15" s="21"/>
+      <c r="S15" s="21"/>
+      <c r="T15" s="21"/>
+      <c r="U15" s="15"/>
+      <c r="V15" s="15"/>
+      <c r="W15" s="15"/>
+      <c r="X15" s="15"/>
+      <c r="Z15" s="8">
+        <v>1</v>
+      </c>
+      <c r="AA15" s="8">
+        <v>2</v>
+      </c>
+      <c r="AB15" s="8">
+        <v>3</v>
+      </c>
+      <c r="AC15" s="8">
+        <v>4</v>
+      </c>
+      <c r="AD15" s="8">
+        <v>5</v>
+      </c>
+      <c r="AE15" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="AG15" s="19">
+        <v>1</v>
+      </c>
+      <c r="AH15" s="19"/>
+      <c r="AI15" s="19">
+        <v>2</v>
+      </c>
+      <c r="AJ15" s="19"/>
+      <c r="AK15" s="19">
+        <v>3</v>
+      </c>
+      <c r="AL15" s="19"/>
+      <c r="AM15" s="19">
+        <v>4</v>
+      </c>
+      <c r="AN15" s="19"/>
+      <c r="AO15" s="19">
+        <v>5</v>
+      </c>
+      <c r="AP15" s="19"/>
+      <c r="AR15" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="AS15" s="39" t="s">
+        <v>33</v>
+      </c>
+      <c r="AT15" s="39"/>
+      <c r="AU15" s="39"/>
+      <c r="AV15" s="40"/>
+      <c r="AW15" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="AX15" s="18"/>
+      <c r="AZ15" s="37"/>
+      <c r="BA15" s="38"/>
+    </row>
+    <row r="16" spans="1:53" ht="87" x14ac:dyDescent="0.35">
+      <c r="A16" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I16" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="J16" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="K16" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="L16" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="M16" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="N16" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P16" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q16" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="R16" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="S16" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="T16" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="U16" s="25"/>
+      <c r="V16" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="W16" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="X16" s="25"/>
+      <c r="Z16" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA16" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB16" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC16" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD16" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE16" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG16" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH16" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AI16" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ16" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AK16" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL16" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AM16" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN16" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AO16" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP16" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AR16" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="AS16" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="AT16" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="AU16" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="AV16" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="AW16" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="AX16" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="AZ16" s="38"/>
+      <c r="BA16" s="38"/>
+    </row>
+    <row r="17" spans="1:53" x14ac:dyDescent="0.35">
+      <c r="A17" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B17" s="27">
+        <v>0</v>
+      </c>
+      <c r="C17" s="8">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="D17" s="27">
+        <f xml:space="preserve"> - 45*LN(1-C17)</f>
+        <v>36.944124843142362</v>
+      </c>
+      <c r="E17" s="28">
+        <f>B17+D17</f>
+        <v>36.944124843142362</v>
+      </c>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="30"/>
+      <c r="J17" s="30"/>
+      <c r="K17" s="30"/>
+      <c r="L17" s="30"/>
+      <c r="M17" s="8"/>
+      <c r="N17" s="8"/>
+      <c r="O17" s="8"/>
+      <c r="P17" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q17" s="8">
+        <v>0</v>
+      </c>
+      <c r="R17" s="8">
+        <v>0</v>
+      </c>
+      <c r="S17" s="8">
+        <v>0</v>
+      </c>
+      <c r="T17" s="8"/>
+      <c r="V17" s="8">
+        <v>0</v>
+      </c>
+      <c r="W17" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="8"/>
+      <c r="AA17" s="8"/>
+      <c r="AB17" s="8"/>
+      <c r="AC17" s="8"/>
+      <c r="AD17" s="8"/>
+      <c r="AE17" s="8"/>
+      <c r="AG17" s="8"/>
+      <c r="AH17" s="8"/>
+      <c r="AI17" s="8"/>
+      <c r="AJ17" s="8"/>
+      <c r="AK17" s="8"/>
+      <c r="AL17" s="8"/>
+      <c r="AM17" s="8"/>
+      <c r="AN17" s="8"/>
+      <c r="AO17" s="8"/>
+      <c r="AP17" s="8"/>
+    </row>
+    <row r="18" spans="1:53" x14ac:dyDescent="0.35">
+      <c r="A18" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="27">
+        <f>E17</f>
+        <v>36.944124843142362</v>
+      </c>
+      <c r="C18" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="D18" s="27">
+        <f xml:space="preserve"> - 45*LN(1-C18)</f>
+        <v>12.94569326033014</v>
+      </c>
+      <c r="E18" s="29">
+        <f>B18+D18</f>
+        <v>49.8898181034725</v>
+      </c>
+      <c r="F18" s="8">
+        <v>0.76</v>
+      </c>
+      <c r="G18" s="27">
+        <f xml:space="preserve"> 10 + F18*(20-10)</f>
+        <v>17.600000000000001</v>
+      </c>
+      <c r="H18" s="28">
+        <f>B18+G18</f>
+        <v>54.544124843142363</v>
+      </c>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
+      <c r="K18" s="31"/>
+      <c r="L18" s="31"/>
+      <c r="M18" s="8"/>
+      <c r="N18" s="8"/>
+      <c r="O18" s="8"/>
+      <c r="P18" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q18" s="8">
+        <v>0</v>
+      </c>
+      <c r="R18" s="8">
+        <v>0</v>
+      </c>
+      <c r="S18" s="8">
+        <v>0</v>
+      </c>
+      <c r="T18" s="8"/>
+      <c r="V18" s="8"/>
+      <c r="W18" s="8"/>
+      <c r="Z18" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA18" s="8"/>
+      <c r="AB18" s="8"/>
+      <c r="AC18" s="8"/>
+      <c r="AD18" s="8"/>
+      <c r="AE18" s="8"/>
+      <c r="AG18" s="8"/>
+      <c r="AH18" s="8"/>
+      <c r="AI18" s="8"/>
+      <c r="AJ18" s="8"/>
+      <c r="AK18" s="8"/>
+      <c r="AL18" s="8"/>
+      <c r="AM18" s="8"/>
+      <c r="AN18" s="8"/>
+      <c r="AO18" s="8"/>
+      <c r="AP18" s="8"/>
+      <c r="BA18" s="15"/>
+    </row>
+    <row r="19" spans="1:53" x14ac:dyDescent="0.35">
+      <c r="A19" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="8"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="27"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="34">
+        <f>0.52</f>
+        <v>0.52</v>
+      </c>
+      <c r="J19" s="31" t="str">
+        <f>IF(I19&lt;G8,E8,E9)</f>
+        <v>No</v>
+      </c>
+      <c r="K19" s="30"/>
+      <c r="L19" s="30"/>
+      <c r="M19" s="8"/>
+      <c r="N19" s="8"/>
+      <c r="O19" s="8"/>
+      <c r="P19" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q19" s="6">
+        <v>0</v>
+      </c>
+      <c r="R19" s="8">
+        <v>1</v>
+      </c>
+      <c r="S19" s="8">
+        <v>0</v>
+      </c>
+      <c r="T19" s="8"/>
+      <c r="V19" s="8"/>
+      <c r="W19" s="8"/>
+      <c r="Z19" s="35"/>
+      <c r="AA19" s="8"/>
+      <c r="AB19" s="8"/>
+      <c r="AC19" s="8"/>
+      <c r="AD19" s="8"/>
+      <c r="AE19" s="8"/>
+      <c r="AG19" s="8"/>
+      <c r="AH19" s="8"/>
+      <c r="AI19" s="8"/>
+      <c r="AJ19" s="8"/>
+      <c r="AK19" s="8"/>
+      <c r="AL19" s="8"/>
+      <c r="AM19" s="8"/>
+      <c r="AN19" s="8"/>
+      <c r="AO19" s="8"/>
+      <c r="AP19" s="8"/>
+    </row>
+    <row r="20" spans="1:53" x14ac:dyDescent="0.35">
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="27"/>
+      <c r="D20" s="27"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="27"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="30"/>
+      <c r="J20" s="30"/>
+      <c r="K20" s="30"/>
+      <c r="L20" s="30"/>
+      <c r="M20" s="8"/>
+      <c r="N20" s="8"/>
+      <c r="O20" s="8"/>
+      <c r="P20" s="8"/>
+      <c r="Q20" s="8"/>
+      <c r="R20" s="8"/>
+      <c r="S20" s="8"/>
+      <c r="T20" s="8"/>
+      <c r="V20" s="8"/>
+      <c r="W20" s="8"/>
+      <c r="Z20" s="8"/>
+      <c r="AA20" s="8"/>
+      <c r="AB20" s="8"/>
+      <c r="AC20" s="8"/>
+      <c r="AD20" s="8"/>
+      <c r="AE20" s="8"/>
+      <c r="AG20" s="8"/>
+      <c r="AH20" s="8"/>
+      <c r="AI20" s="8"/>
+      <c r="AJ20" s="8"/>
+      <c r="AK20" s="8"/>
+      <c r="AL20" s="8"/>
+      <c r="AM20" s="8"/>
+      <c r="AN20" s="8"/>
+      <c r="AO20" s="8"/>
+      <c r="AP20" s="8"/>
+    </row>
+    <row r="21" spans="1:53" x14ac:dyDescent="0.35">
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="27"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="30"/>
+      <c r="J21" s="30"/>
+      <c r="K21" s="30"/>
+      <c r="L21" s="30"/>
+      <c r="M21" s="8"/>
+      <c r="N21" s="8"/>
+      <c r="O21" s="8"/>
+      <c r="P21" s="8"/>
+      <c r="Q21" s="8"/>
+      <c r="R21" s="8"/>
+      <c r="S21" s="8"/>
+      <c r="T21" s="8"/>
+      <c r="V21" s="8"/>
+      <c r="W21" s="8"/>
+      <c r="Z21" s="8"/>
+      <c r="AA21" s="8"/>
+      <c r="AB21" s="8"/>
+      <c r="AC21" s="8"/>
+      <c r="AD21" s="8"/>
+      <c r="AE21" s="8"/>
+      <c r="AG21" s="8"/>
+      <c r="AH21" s="8"/>
+      <c r="AI21" s="8"/>
+      <c r="AJ21" s="8"/>
+      <c r="AK21" s="8"/>
+      <c r="AL21" s="8"/>
+      <c r="AM21" s="8"/>
+      <c r="AN21" s="8"/>
+      <c r="AO21" s="8"/>
+      <c r="AP21" s="8"/>
+    </row>
+    <row r="22" spans="1:53" x14ac:dyDescent="0.35">
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="27"/>
+      <c r="D22" s="27"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="27"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="30"/>
+      <c r="J22" s="30"/>
+      <c r="K22" s="30"/>
+      <c r="L22" s="30"/>
+      <c r="M22" s="8"/>
+      <c r="N22" s="8"/>
+      <c r="O22" s="8"/>
+      <c r="P22" s="8"/>
+      <c r="Q22" s="8"/>
+      <c r="R22" s="8"/>
+      <c r="S22" s="8"/>
+      <c r="T22" s="8"/>
+      <c r="V22" s="8"/>
+      <c r="W22" s="8"/>
+      <c r="Z22" s="8"/>
+      <c r="AA22" s="8"/>
+      <c r="AB22" s="8"/>
+      <c r="AC22" s="8"/>
+      <c r="AD22" s="8"/>
+      <c r="AE22" s="8"/>
+      <c r="AG22" s="8"/>
+      <c r="AH22" s="8"/>
+      <c r="AI22" s="8"/>
+      <c r="AJ22" s="8"/>
+      <c r="AK22" s="8"/>
+      <c r="AL22" s="8"/>
+      <c r="AM22" s="8"/>
+      <c r="AN22" s="8"/>
+      <c r="AO22" s="8"/>
+      <c r="AP22" s="8"/>
+    </row>
+    <row r="23" spans="1:53" x14ac:dyDescent="0.35">
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="27"/>
+      <c r="D23" s="27"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="27"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="30"/>
+      <c r="J23" s="30"/>
+      <c r="K23" s="30"/>
+      <c r="L23" s="30"/>
+      <c r="M23" s="8"/>
+      <c r="N23" s="8"/>
+      <c r="O23" s="8"/>
+      <c r="P23" s="8"/>
+      <c r="Q23" s="8"/>
+      <c r="R23" s="8"/>
+      <c r="S23" s="8"/>
+      <c r="T23" s="8"/>
+      <c r="V23" s="8"/>
+      <c r="W23" s="8"/>
+      <c r="Z23" s="8"/>
+      <c r="AA23" s="8"/>
+      <c r="AB23" s="8"/>
+      <c r="AC23" s="8"/>
+      <c r="AD23" s="8"/>
+      <c r="AE23" s="8"/>
+      <c r="AG23" s="8"/>
+      <c r="AH23" s="8"/>
+      <c r="AI23" s="8"/>
+      <c r="AJ23" s="8"/>
+      <c r="AK23" s="8"/>
+      <c r="AL23" s="8"/>
+      <c r="AM23" s="8"/>
+      <c r="AN23" s="8"/>
+      <c r="AO23" s="8"/>
+      <c r="AP23" s="8"/>
+    </row>
+    <row r="24" spans="1:53" x14ac:dyDescent="0.35">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="27"/>
+      <c r="D24" s="27"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="27"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="30"/>
+      <c r="J24" s="30"/>
+      <c r="K24" s="30"/>
+      <c r="L24" s="30"/>
+      <c r="M24" s="8"/>
+      <c r="N24" s="8"/>
+      <c r="O24" s="8"/>
+      <c r="P24" s="8"/>
+      <c r="Q24" s="8"/>
+      <c r="R24" s="8"/>
+      <c r="S24" s="8"/>
+      <c r="T24" s="8"/>
+      <c r="V24" s="8"/>
+      <c r="W24" s="8"/>
+      <c r="Z24" s="8"/>
+      <c r="AA24" s="8"/>
+      <c r="AB24" s="8"/>
+      <c r="AC24" s="8"/>
+      <c r="AD24" s="8"/>
+      <c r="AE24" s="8"/>
+      <c r="AG24" s="8"/>
+      <c r="AH24" s="8"/>
+      <c r="AI24" s="8"/>
+      <c r="AJ24" s="8"/>
+      <c r="AK24" s="8"/>
+      <c r="AL24" s="8"/>
+      <c r="AM24" s="8"/>
+      <c r="AN24" s="8"/>
+      <c r="AO24" s="8"/>
+      <c r="AP24" s="8"/>
+    </row>
+    <row r="25" spans="1:53" x14ac:dyDescent="0.35">
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="27"/>
+      <c r="D25" s="27"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="27"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="30"/>
+      <c r="J25" s="30"/>
+      <c r="K25" s="30"/>
+      <c r="L25" s="30"/>
+      <c r="M25" s="8"/>
+      <c r="N25" s="8"/>
+      <c r="O25" s="8"/>
+      <c r="P25" s="8"/>
+      <c r="Q25" s="8"/>
+      <c r="R25" s="8"/>
+      <c r="S25" s="8"/>
+      <c r="T25" s="8"/>
+      <c r="V25" s="8"/>
+      <c r="W25" s="8"/>
+      <c r="Z25" s="8"/>
+      <c r="AA25" s="8"/>
+      <c r="AB25" s="8"/>
+      <c r="AC25" s="8"/>
+      <c r="AD25" s="8"/>
+      <c r="AE25" s="8"/>
+      <c r="AG25" s="8"/>
+      <c r="AH25" s="8"/>
+      <c r="AI25" s="8"/>
+      <c r="AJ25" s="8"/>
+      <c r="AK25" s="8"/>
+      <c r="AL25" s="8"/>
+      <c r="AM25" s="8"/>
+      <c r="AN25" s="8"/>
+      <c r="AO25" s="8"/>
+      <c r="AP25" s="8"/>
+    </row>
+    <row r="26" spans="1:53" x14ac:dyDescent="0.35">
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="27"/>
+      <c r="D26" s="27"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="27"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="30"/>
+      <c r="J26" s="30"/>
+      <c r="K26" s="30"/>
+      <c r="L26" s="30"/>
+      <c r="M26" s="8"/>
+      <c r="N26" s="8"/>
+      <c r="O26" s="8"/>
+      <c r="P26" s="8"/>
+      <c r="Q26" s="8"/>
+      <c r="R26" s="8"/>
+      <c r="S26" s="8"/>
+      <c r="T26" s="8"/>
+      <c r="V26" s="8"/>
+      <c r="W26" s="8"/>
+      <c r="Z26" s="8"/>
+      <c r="AA26" s="8"/>
+      <c r="AB26" s="8"/>
+      <c r="AC26" s="8"/>
+      <c r="AD26" s="8"/>
+      <c r="AE26" s="8"/>
+      <c r="AG26" s="8"/>
+      <c r="AH26" s="8"/>
+      <c r="AI26" s="8"/>
+      <c r="AJ26" s="8"/>
+      <c r="AK26" s="8"/>
+      <c r="AL26" s="8"/>
+      <c r="AM26" s="8"/>
+      <c r="AN26" s="8"/>
+      <c r="AO26" s="8"/>
+      <c r="AP26" s="8"/>
+    </row>
+    <row r="27" spans="1:53" x14ac:dyDescent="0.35">
+      <c r="C27" s="11"/>
+      <c r="G27" s="11"/>
+    </row>
+    <row r="28" spans="1:53" x14ac:dyDescent="0.35">
+      <c r="C28" s="11"/>
+      <c r="G28" s="11"/>
+    </row>
+    <row r="29" spans="1:53" x14ac:dyDescent="0.35">
+      <c r="C29" s="11"/>
+      <c r="G29" s="11"/>
+    </row>
+    <row r="30" spans="1:53" x14ac:dyDescent="0.35">
+      <c r="C30" s="11"/>
+      <c r="G30" s="11"/>
+    </row>
+    <row r="31" spans="1:53" x14ac:dyDescent="0.35">
+      <c r="C31" s="11"/>
+      <c r="G31" s="11"/>
+    </row>
+    <row r="32" spans="1:53" x14ac:dyDescent="0.35">
+      <c r="C32" s="11"/>
+      <c r="G32" s="11"/>
+    </row>
+    <row r="33" spans="3:7" x14ac:dyDescent="0.35">
+      <c r="C33" s="11"/>
+      <c r="G33" s="11"/>
+    </row>
+    <row r="34" spans="3:7" x14ac:dyDescent="0.35">
+      <c r="C34" s="11"/>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="AK15:AL15"/>
+    <mergeCell ref="AM15:AN15"/>
+    <mergeCell ref="AO15:AP15"/>
+    <mergeCell ref="AS15:AV15"/>
+    <mergeCell ref="AW15:AX15"/>
+    <mergeCell ref="AG15:AH15"/>
+    <mergeCell ref="P15:T15"/>
+    <mergeCell ref="AI15:AJ15"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="M15:O15"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F392AB3F-D6B3-4AD6-8101-AA40A564585E}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
